--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_381_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_381_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>24</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>8</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>32:24</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>63:22</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>30:37</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>70:54</t>
+          <t>30:09</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,12 +2235,12 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2315,10 +2315,10 @@
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>26:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>30:43</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>69:39</t>
+          <t>28:54</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>30:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>26:27</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>105</v>
       </c>
       <c r="T30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>40:50</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>74:00</t>
+          <t>33:13</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>2</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>38:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -4880,16 +4880,16 @@
         <v>16</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>6</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>57:57</t>
+          <t>27:09</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -5079,13 +5079,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>37:39</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,17 +5192,17 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>28:24</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>47:47</t>
+          <t>27:01</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -5664,16 +5664,16 @@
         <v>29</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>5</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>78:59</t>
+          <t>38:12</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -6000,16 +6000,16 @@
         <v>90</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="W44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>30</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_381_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_381_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>24</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>8</v>
@@ -1727,10 +1727,10 @@
         <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>105</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>2</v>
@@ -4880,16 +4880,16 @@
         <v>16</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>6</v>
@@ -5079,13 +5079,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>5</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5664,16 +5664,16 @@
         <v>29</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>5</v>
@@ -6000,16 +6000,16 @@
         <v>90</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X44" t="n">
         <v>30</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_381_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_381_EL.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
         <v>9</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
         <v>7</v>
@@ -854,17 +854,17 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
         <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y26" t="n">
         <v>6</v>
       </c>
-      <c r="Y26" t="n">
-        <v>7</v>
-      </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3839,14 +3839,14 @@
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="Y30" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y36" t="n">
         <v>4</v>
       </c>
-      <c r="Y36" t="n">
-        <v>5</v>
-      </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,10 +4892,10 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,10 +5676,10 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6012,14 +6012,14 @@
         <v>7</v>
       </c>
       <c r="X44" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6048,22 +6048,22 @@
         <v>3</v>
       </c>
       <c r="AH44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ44" t="n">
         <v>4</v>
       </c>
       <c r="AK44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
